--- a/outputs/Modelo_financiero.xlsx
+++ b/outputs/Modelo_financiero.xlsx
@@ -828,7 +828,7 @@
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>Cobro = ventas de hace «días de cobro» meses. Fianzas de cumplimiento sobre la cantidad máxima del contrato (30% LPU, 20% MINSA), vigentes 3 meses (LPU) o 6 (MINSA) después de cada contrato; fianza de propuesta de 10% en la LPU para renglones de más de B/.70,000; el colateral queda inmovilizado.</t>
+          <t>Cobro = ventas de hace «días de cobro» meses. Fianzas de cumplimiento sobre la cantidad máxima del contrato (30% LPU, 20% MINSA), vigentes 3 meses (LPU) o 6 (MINSA) después de cada contrato; fianza de propuesta de 10% sobre toda la oferta en la LPU (el acto supera B/.70,000: Ley 419, art. 245); el colateral queda inmovilizado.</t>
         </is>
       </c>
     </row>
@@ -880,7 +880,7 @@
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>La fábrica no ha dado precios: el costo parte de una referencia por producto = precio de compra pública en India x 1.4, multiplicada por el índice del proveedor (1.25 en la base).</t>
+          <t>La fábrica no ha dado precios: el costo parte de una referencia por producto = precio representativo de las compras públicas indias vigentes x 1.4 (ajustado en cinco productos; ver la columna de fuente en Productos), multiplicada por el índice del proveedor (1.25 en la base).</t>
         </is>
       </c>
     </row>
@@ -2465,7 +2465,7 @@
       </c>
       <c r="B40" s="12" t="inlineStr">
         <is>
-          <t>Fianza de propuesta en la LPU (% de la oferta, renglones con referencia mayor de B/.70,000)</t>
+          <t>Fianza de propuesta en la LPU (% de toda la oferta: el acto supera B/.70,000, Ley 419 art. 245)</t>
         </is>
       </c>
       <c r="C40" s="9" t="inlineStr">
@@ -5417,7 +5417,7 @@
       </c>
       <c r="G6" s="12" t="inlineStr">
         <is>
-          <t>R: PMBI 2024-27 INR 2.74 por 10 x1.4; blíster 5.5 cm3</t>
+          <t>R: PMBI 2024-27 INR 2.74 por 10, TNMSC 2024 INR 23.48 por 100 y Assam 2025 INR 2.50 por 10; x1.4 = US$0.0034-0.0040; se usa 0.0038; blíster 5.5 cm3</t>
         </is>
       </c>
       <c r="H6" s="16" t="n">
@@ -5541,7 +5541,7 @@
         <v/>
       </c>
       <c r="AN6" s="14">
-        <f>IF(AND(Y6=1,H6*I6*15/12&gt;70000),H6*p_mkt*Q6*p_rs_succ,0)</f>
+        <f>IF(AND(Y6=1,H6&gt;0),H6*p_mkt*Q6*p_rs_succ,0)</f>
         <v/>
       </c>
     </row>
@@ -5572,7 +5572,7 @@
       </c>
       <c r="G7" s="12" t="inlineStr">
         <is>
-          <t>R: TNMSC 2024 L1 INR 5.72 por 60 ml escalado a 120 ml, x1.4; 450 cm3</t>
+          <t>R: TNMSC 2024 INR 5.72 y Assam 2025 INR 5.85 por 60 ml; a 120 ml se usa INR 10.2 (factor 1.75 por frasco más grande), x1.4; 450 cm3</t>
         </is>
       </c>
       <c r="H7" s="16" t="n">
@@ -5696,7 +5696,7 @@
         <v/>
       </c>
       <c r="AN7" s="14">
-        <f>IF(AND(Y7=1,H7*I7*15/12&gt;70000),H7*p_mkt*Q7*p_rs_succ,0)</f>
+        <f>IF(AND(Y7=1,H7&gt;0),H7*p_mkt*Q7*p_rs_succ,0)</f>
         <v/>
       </c>
     </row>
@@ -5727,7 +5727,7 @@
       </c>
       <c r="G8" s="12" t="inlineStr">
         <is>
-          <t>R: PMBI 2024-26 INR 31.60 por 6 x1.4; alu-alu 12 cm3</t>
+          <t>R: PMBI 2024-26 INR 31.60 por 6 y TNMSC 2024 INR 30.81 por 6 (se usa INR 5.2 por tableta), x1.4; alu-alu 12 cm3</t>
         </is>
       </c>
       <c r="H8" s="16" t="n">
@@ -5852,7 +5852,7 @@
         <v/>
       </c>
       <c r="AN8" s="14">
-        <f>IF(AND(Y8=1,H8*I8*15/12&gt;70000),H8*p_mkt*Q8*p_rs_succ,0)</f>
+        <f>IF(AND(Y8=1,H8&gt;0),H8*p_mkt*Q8*p_rs_succ,0)</f>
         <v/>
       </c>
     </row>
@@ -5883,7 +5883,7 @@
       </c>
       <c r="G9" s="12" t="inlineStr">
         <is>
-          <t>R: PMBI 2023-26 INR 28.06 por 30 ml escalado a 100 ml, x1.4; 500 cm3</t>
+          <t>R: PMBI 2023-26 INR 28.06 por 30 ml, escalado a 100 ml (x2.85 = INR 80), x1.4; 500 cm3</t>
         </is>
       </c>
       <c r="H9" s="16" t="n">
@@ -6007,7 +6007,7 @@
         <v/>
       </c>
       <c r="AN9" s="14">
-        <f>IF(AND(Y9=1,H9*I9*15/12&gt;70000),H9*p_mkt*Q9*p_rs_succ,0)</f>
+        <f>IF(AND(Y9=1,H9&gt;0),H9*p_mkt*Q9*p_rs_succ,0)</f>
         <v/>
       </c>
     </row>
@@ -6038,7 +6038,7 @@
       </c>
       <c r="G10" s="12" t="inlineStr">
         <is>
-          <t>R: Assam 2025 INR 12.6 por vial x1.4; 54 cm3</t>
+          <t>R: Assam 2025 INR 12.6 y Delhi 2022 INR 15.48 por vial; se usa INR 13.5, x1.4; 54 cm3</t>
         </is>
       </c>
       <c r="H10" s="16" t="n">
@@ -6163,7 +6163,7 @@
         <v/>
       </c>
       <c r="AN10" s="14">
-        <f>IF(AND(Y10=1,H10*I10*15/12&gt;70000),H10*p_mkt*Q10*p_rs_succ,0)</f>
+        <f>IF(AND(Y10=1,H10&gt;0),H10*p_mkt*Q10*p_rs_succ,0)</f>
         <v/>
       </c>
     </row>
@@ -6194,7 +6194,7 @@
       </c>
       <c r="G11" s="12" t="inlineStr">
         <is>
-          <t>R: Assam 2025 INR 13.3 por vial x1.4; 54 cm3</t>
+          <t>R: Assam 2025 INR 13.3 por vial (PMBI 500 mg con agua INR 12.32); se usa INR 14.0, x1.4; 54 cm3</t>
         </is>
       </c>
       <c r="H11" s="16" t="n">
@@ -6319,7 +6319,7 @@
         <v/>
       </c>
       <c r="AN11" s="14">
-        <f>IF(AND(Y11=1,H11*I11*15/12&gt;70000),H11*p_mkt*Q11*p_rs_succ,0)</f>
+        <f>IF(AND(Y11=1,H11&gt;0),H11*p_mkt*Q11*p_rs_succ,0)</f>
         <v/>
       </c>
     </row>
@@ -6350,7 +6350,7 @@
       </c>
       <c r="G12" s="12" t="inlineStr">
         <is>
-          <t>R: PMBI 2022-25 INR 4.22 por 10 ml x1.4; 80 cm3 (el ganador de la LPU entregó 20 ml)</t>
+          <t>R: PMBI 2022-25 INR 4.22 y Delhi 2022 INR 4.59 por 10 ml; x1.4 = US$0.062; se usa 0.07; 80 cm3 (el ganador de la LPU entregó 20 ml)</t>
         </is>
       </c>
       <c r="H12" s="16" t="n">
@@ -6475,7 +6475,7 @@
         <v/>
       </c>
       <c r="AN12" s="14">
-        <f>IF(AND(Y12=1,H12*I12*15/12&gt;70000),H12*p_mkt*Q12*p_rs_succ,0)</f>
+        <f>IF(AND(Y12=1,H12&gt;0),H12*p_mkt*Q12*p_rs_succ,0)</f>
         <v/>
       </c>
     </row>
@@ -6506,7 +6506,7 @@
       </c>
       <c r="G13" s="12" t="inlineStr">
         <is>
-          <t>R: sin licitación india pública; MRP de Jan Aushadhi x0.42 x1.4; 3 cm3</t>
+          <t>R: sin licitación india pública; precio al público de Jan Aushadhi INR 8.44 por 6 x0.42 = INR 0.59, x1.4; 3 cm3</t>
         </is>
       </c>
       <c r="H13" s="16" t="n">
@@ -6631,7 +6631,7 @@
         <v/>
       </c>
       <c r="AN13" s="14">
-        <f>IF(AND(Y13=1,H13*I13*15/12&gt;70000),H13*p_mkt*Q13*p_rs_succ,0)</f>
+        <f>IF(AND(Y13=1,H13&gt;0),H13*p_mkt*Q13*p_rs_succ,0)</f>
         <v/>
       </c>
     </row>
@@ -6662,7 +6662,7 @@
       </c>
       <c r="G14" s="12" t="inlineStr">
         <is>
-          <t>R: sin precio indio público; UNICEF US$0.60 por 30 ml como techo; 185 cm3</t>
+          <t>R: sin precio indio público; se usa US$0.42 con UNICEF US$0.60 por 30 ml como techo; 185 cm3</t>
         </is>
       </c>
       <c r="H14" s="16" t="n">
@@ -6787,7 +6787,7 @@
         <v/>
       </c>
       <c r="AN14" s="14">
-        <f>IF(AND(Y14=1,H14*I14*15/12&gt;70000),H14*p_mkt*Q14*p_rs_succ,0)</f>
+        <f>IF(AND(Y14=1,H14&gt;0),H14*p_mkt*Q14*p_rs_succ,0)</f>
         <v/>
       </c>
     </row>
@@ -6943,7 +6943,7 @@
         <v/>
       </c>
       <c r="AN15" s="14">
-        <f>IF(AND(Y15=1,H15*I15*15/12&gt;70000),H15*p_mkt*Q15*p_rs_succ,0)</f>
+        <f>IF(AND(Y15=1,H15&gt;0),H15*p_mkt*Q15*p_rs_succ,0)</f>
         <v/>
       </c>
     </row>
@@ -6974,7 +6974,7 @@
       </c>
       <c r="G16" s="12" t="inlineStr">
         <is>
-          <t>R: PMBI 2023-25 INR 6.00 por tubo x1.4 (redondeado); 110 cm3</t>
+          <t>R: PMBI 2023-25 INR 6.00 por tubo; x1.4 = US$0.087; se usa 0.10; 110 cm3</t>
         </is>
       </c>
       <c r="H16" s="16" t="n">
@@ -7099,7 +7099,7 @@
         <v/>
       </c>
       <c r="AN16" s="14">
-        <f>IF(AND(Y16=1,H16*I16*15/12&gt;70000),H16*p_mkt*Q16*p_rs_succ,0)</f>
+        <f>IF(AND(Y16=1,H16&gt;0),H16*p_mkt*Q16*p_rs_succ,0)</f>
         <v/>
       </c>
     </row>
@@ -7130,7 +7130,7 @@
       </c>
       <c r="G17" s="12" t="inlineStr">
         <is>
-          <t>R: PMBI 2023-25 INR 1.99 por 10 x1.4</t>
+          <t>R: Assam 2025 INR 1.90 por 10 (PMBI INR 1.99; TNMSC INR 1.71), x1.4</t>
         </is>
       </c>
       <c r="H17" s="16" t="n">
@@ -7255,7 +7255,7 @@
         <v/>
       </c>
       <c r="AN17" s="14">
-        <f>IF(AND(Y17=1,H17*I17*15/12&gt;70000),H17*p_mkt*Q17*p_rs_succ,0)</f>
+        <f>IF(AND(Y17=1,H17&gt;0),H17*p_mkt*Q17*p_rs_succ,0)</f>
         <v/>
       </c>
     </row>
@@ -7286,7 +7286,7 @@
       </c>
       <c r="G18" s="12" t="inlineStr">
         <is>
-          <t>R: TNMSC 2024 L1 INR 19.63 por 100 x1.4</t>
+          <t>R: Assam 2025 INR 2.30 por 10 (TNMSC INR 19.63 por 100; PMBI INR 3.49 por 15), x1.4</t>
         </is>
       </c>
       <c r="H18" s="16" t="n">
@@ -7410,7 +7410,7 @@
         <v/>
       </c>
       <c r="AN18" s="14">
-        <f>IF(AND(Y18=1,H18*I18*15/12&gt;70000),H18*p_mkt*Q18*p_rs_succ,0)</f>
+        <f>IF(AND(Y18=1,H18&gt;0),H18*p_mkt*Q18*p_rs_succ,0)</f>
         <v/>
       </c>
     </row>
@@ -7565,7 +7565,7 @@
         <v/>
       </c>
       <c r="AN19" s="14">
-        <f>IF(AND(Y19=1,H19*I19*15/12&gt;70000),H19*p_mkt*Q19*p_rs_succ,0)</f>
+        <f>IF(AND(Y19=1,H19&gt;0),H19*p_mkt*Q19*p_rs_succ,0)</f>
         <v/>
       </c>
     </row>
@@ -7720,7 +7720,7 @@
         <v/>
       </c>
       <c r="AN20" s="14">
-        <f>IF(AND(Y20=1,H20*I20*15/12&gt;70000),H20*p_mkt*Q20*p_rs_succ,0)</f>
+        <f>IF(AND(Y20=1,H20&gt;0),H20*p_mkt*Q20*p_rs_succ,0)</f>
         <v/>
       </c>
     </row>
@@ -7875,7 +7875,7 @@
         <v/>
       </c>
       <c r="AN21" s="14">
-        <f>IF(AND(Y21=1,H21*I21*15/12&gt;70000),H21*p_mkt*Q21*p_rs_succ,0)</f>
+        <f>IF(AND(Y21=1,H21&gt;0),H21*p_mkt*Q21*p_rs_succ,0)</f>
         <v/>
       </c>
     </row>
@@ -8030,7 +8030,7 @@
         <v/>
       </c>
       <c r="AN22" s="14">
-        <f>IF(AND(Y22=1,H22*I22*15/12&gt;70000),H22*p_mkt*Q22*p_rs_succ,0)</f>
+        <f>IF(AND(Y22=1,H22&gt;0),H22*p_mkt*Q22*p_rs_succ,0)</f>
         <v/>
       </c>
     </row>
@@ -22072,7 +22072,7 @@
         <v>-95535.94740008263</v>
       </c>
       <c r="E9" s="14" t="n">
-        <v>-56881.19066947518</v>
+        <v>-56975.84524326061</v>
       </c>
     </row>
     <row r="10">
@@ -22082,13 +22082,13 @@
         </is>
       </c>
       <c r="C10" s="14" t="n">
-        <v>-95787.96219041818</v>
+        <v>-95850.47493266819</v>
       </c>
       <c r="D10" s="14" t="n">
-        <v>8283.487125985275</v>
+        <v>8147.931080925095</v>
       </c>
       <c r="E10" s="14" t="n">
-        <v>420570.583153204</v>
+        <v>420522.072684139</v>
       </c>
     </row>
     <row r="11">
@@ -22098,13 +22098,13 @@
         </is>
       </c>
       <c r="C11" s="14" t="n">
-        <v>-98032.43983874223</v>
+        <v>-98157.46532324223</v>
       </c>
       <c r="D11" s="14" t="n">
-        <v>13802.81663612504</v>
+        <v>13727.89111303723</v>
       </c>
       <c r="E11" s="14" t="n">
-        <v>459424.9247733059</v>
+        <v>459281.2219203771</v>
       </c>
     </row>
     <row r="12">
@@ -22114,13 +22114,13 @@
         </is>
       </c>
       <c r="C12" s="14" t="n">
-        <v>591336.1711870213</v>
+        <v>591968.850148785</v>
       </c>
       <c r="D12" s="14" t="n">
-        <v>388711.4774327216</v>
+        <v>392937.988920986</v>
       </c>
       <c r="E12" s="14" t="n">
-        <v>199834.6570402177</v>
+        <v>196374.2135548402</v>
       </c>
     </row>
     <row r="13">
@@ -22133,10 +22133,10 @@
         <v>60</v>
       </c>
       <c r="D13" s="28" t="n">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="E13" s="28" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
     </row>
     <row r="14">
@@ -22146,13 +22146,13 @@
         </is>
       </c>
       <c r="C14" s="14" t="n">
-        <v>-434114.901517554</v>
+        <v>-435375.3149837715</v>
       </c>
       <c r="D14" s="14" t="n">
-        <v>-196169.2184459174</v>
+        <v>-198692.758921373</v>
       </c>
       <c r="E14" s="14" t="n">
-        <v>601365.7335600459</v>
+        <v>600643.0239782698</v>
       </c>
     </row>
     <row r="15">
@@ -22162,13 +22162,13 @@
         </is>
       </c>
       <c r="C15" s="14" t="n">
-        <v>-357953.4512924972</v>
+        <v>-359335.1517915485</v>
       </c>
       <c r="D15" s="14" t="n">
-        <v>-204909.441398624</v>
+        <v>-207445.2536953371</v>
       </c>
       <c r="E15" s="14" t="n">
-        <v>298397.7813043951</v>
+        <v>297569.6445991886</v>
       </c>
     </row>
     <row r="16">
@@ -22178,13 +22178,13 @@
         </is>
       </c>
       <c r="C16" s="20" t="n">
-        <v>-0.9586475652022435</v>
+        <v>-0.9484344690969371</v>
       </c>
       <c r="D16" s="20" t="n">
-        <v>-0.122461163731701</v>
+        <v>-0.1231665101213257</v>
       </c>
       <c r="E16" s="20" t="n">
-        <v>0.7896283145803891</v>
+        <v>0.7851602886537286</v>
       </c>
     </row>
     <row r="17">
@@ -22194,13 +22194,13 @@
         </is>
       </c>
       <c r="C17" s="44" t="n">
-        <v>0.04582895818304438</v>
+        <v>0.04577095031400461</v>
       </c>
       <c r="D17" s="44" t="n">
-        <v>0.6349583774023235</v>
+        <v>0.6332683846227841</v>
       </c>
       <c r="E17" s="44" t="n">
-        <v>7.23834776252308</v>
+        <v>7.34528700211265</v>
       </c>
     </row>
     <row r="18">
@@ -22297,16 +22297,16 @@
         </is>
       </c>
       <c r="C25" s="14" t="n">
-        <v>388711.4774327216</v>
+        <v>392937.988920986</v>
       </c>
       <c r="D25" s="14" t="n">
-        <v>-196169.2184459174</v>
+        <v>-198692.758921373</v>
       </c>
       <c r="E25" s="20" t="n">
-        <v>-0.122461163731701</v>
+        <v>-0.1231665101213257</v>
       </c>
       <c r="F25" s="44" t="n">
-        <v>0.6349583774023235</v>
+        <v>0.6332683846227841</v>
       </c>
       <c r="G25" s="14" t="n">
         <v>176158.7977303777</v>
@@ -22319,16 +22319,16 @@
         </is>
       </c>
       <c r="C26" s="14" t="n">
-        <v>346516.4879358903</v>
+        <v>350007.2215238342</v>
       </c>
       <c r="D26" s="14" t="n">
-        <v>-181409.7406591706</v>
+        <v>-183848.576768038</v>
       </c>
       <c r="E26" s="20" t="n">
-        <v>-0.1335886511618876</v>
+        <v>-0.1343838259147169</v>
       </c>
       <c r="F26" s="44" t="n">
-        <v>0.6052752880582062</v>
+        <v>0.6029907493386156</v>
       </c>
       <c r="G26" s="14" t="n">
         <v>176158.7977303777</v>
@@ -22341,16 +22341,16 @@
         </is>
       </c>
       <c r="C27" s="14" t="n">
-        <v>375181.1309235524</v>
+        <v>375529.2595242536</v>
       </c>
       <c r="D27" s="14" t="n">
-        <v>-174057.7097073089</v>
+        <v>-176387.9087602243</v>
       </c>
       <c r="E27" s="20" t="n">
-        <v>-0.08754008931799429</v>
+        <v>-0.08896553656540196</v>
       </c>
       <c r="F27" s="44" t="n">
-        <v>0.7240641681232675</v>
+        <v>0.7181857193050778</v>
       </c>
       <c r="G27" s="14" t="n">
         <v>182698.0722724473</v>
@@ -22363,16 +22363,16 @@
         </is>
       </c>
       <c r="C28" s="14" t="n">
-        <v>338380.8022327216</v>
+        <v>338690.6446214305</v>
       </c>
       <c r="D28" s="14" t="n">
-        <v>-144183.1698959653</v>
+        <v>-146256.8501143093</v>
       </c>
       <c r="E28" s="20" t="n">
-        <v>-0.05952151619340162</v>
+        <v>-0.06100413229000412</v>
       </c>
       <c r="F28" s="44" t="n">
-        <v>0.8040775590844975</v>
+        <v>0.7982033397453905</v>
       </c>
       <c r="G28" s="14" t="n">
         <v>176158.7977303777</v>
@@ -22385,16 +22385,16 @@
         </is>
       </c>
       <c r="C29" s="14" t="n">
-        <v>350259.8231393413</v>
+        <v>351663.2053804731</v>
       </c>
       <c r="D29" s="14" t="n">
-        <v>-183914.3002083317</v>
+        <v>-185533.3936370161</v>
       </c>
       <c r="E29" s="20" t="n">
-        <v>-0.1287980723785256</v>
+        <v>-0.1296408381471202</v>
       </c>
       <c r="F29" s="44" t="n">
-        <v>0.6122783206221087</v>
+        <v>0.6093320554025768</v>
       </c>
       <c r="G29" s="14" t="n">
         <v>176158.7977303777</v>
@@ -22407,16 +22407,16 @@
         </is>
       </c>
       <c r="C30" s="14" t="n">
-        <v>427163.131726102</v>
+        <v>434212.7724614988</v>
       </c>
       <c r="D30" s="14" t="n">
-        <v>-208424.1366835031</v>
+        <v>-211852.12420573</v>
       </c>
       <c r="E30" s="20" t="n">
-        <v>-0.1172254510569052</v>
+        <v>-0.1178646387509127</v>
       </c>
       <c r="F30" s="44" t="n">
-        <v>0.6535552835644449</v>
+        <v>0.6526541023917536</v>
       </c>
       <c r="G30" s="14" t="n">
         <v>176158.7977303777</v>
@@ -22429,16 +22429,16 @@
         </is>
       </c>
       <c r="C31" s="14" t="n">
-        <v>371220.0609974038</v>
+        <v>383615.0173086413</v>
       </c>
       <c r="D31" s="14" t="n">
-        <v>-192199.2100492774</v>
+        <v>-195869.8506610747</v>
       </c>
       <c r="E31" s="20" t="n">
-        <v>-0.1015673556446719</v>
+        <v>-0.1003341367371343</v>
       </c>
       <c r="F31" s="44" t="n">
-        <v>0.6679374020851465</v>
+        <v>0.6744913185755171</v>
       </c>
       <c r="G31" s="14" t="n">
         <v>194082.3479727709</v>
@@ -22451,16 +22451,16 @@
         </is>
       </c>
       <c r="C32" s="14" t="n">
-        <v>384541.5579698699</v>
+        <v>384851.4003585788</v>
       </c>
       <c r="D32" s="14" t="n">
-        <v>-170504.1893428613</v>
+        <v>-172578.1196067595</v>
       </c>
       <c r="E32" s="20" t="n">
-        <v>-0.07359914483366714</v>
+        <v>-0.07487329829830702</v>
       </c>
       <c r="F32" s="44" t="n">
-        <v>0.7637572901235501</v>
+        <v>0.7586201119703216</v>
       </c>
       <c r="G32" s="14" t="n">
         <v>198288.0298225947</v>
@@ -22473,16 +22473,16 @@
         </is>
       </c>
       <c r="C33" s="14" t="n">
-        <v>390487.4382007373</v>
+        <v>391025.6836986788</v>
       </c>
       <c r="D33" s="14" t="n">
-        <v>-144345.0111663217</v>
+        <v>-147736.2054889357</v>
       </c>
       <c r="E33" s="20" t="n">
-        <v>-0.01281081580394039</v>
+        <v>-0.01487380808194994</v>
       </c>
       <c r="F33" s="44" t="n">
-        <v>0.9530188785726266</v>
+        <v>0.9450415288698631</v>
       </c>
       <c r="G33" s="14" t="n">
         <v>247968.6056689775</v>
@@ -22495,16 +22495,16 @@
         </is>
       </c>
       <c r="C34" s="14" t="n">
-        <v>253773.8294139227</v>
+        <v>254121.9580146239</v>
       </c>
       <c r="D34" s="14" t="n">
-        <v>-96773.22011052544</v>
+        <v>-99076.58709069903</v>
       </c>
       <c r="E34" s="20" t="n">
-        <v>-0.04018654649937692</v>
+        <v>-0.04249324295312795</v>
       </c>
       <c r="F34" s="44" t="n">
-        <v>0.8681551033803493</v>
+        <v>0.8594745024144518</v>
       </c>
       <c r="G34" s="14" t="n">
         <v>182698.0722724473</v>
@@ -22517,16 +22517,16 @@
         </is>
       </c>
       <c r="C35" s="14" t="n">
-        <v>206771.1542139227</v>
+        <v>207119.2828146239</v>
       </c>
       <c r="D35" s="14" t="n">
-        <v>-50874.91712709206</v>
+        <v>-54231.91036574621</v>
       </c>
       <c r="E35" s="20" t="n">
-        <v>0.03890061949807633</v>
+        <v>0.03463550243249025</v>
       </c>
       <c r="F35" s="44" t="n">
-        <v>1.141490237558482</v>
+        <v>1.129179385741512</v>
       </c>
       <c r="G35" s="14" t="n">
         <v>182698.0722724473</v>
@@ -22539,16 +22539,16 @@
         </is>
       </c>
       <c r="C36" s="14" t="n">
-        <v>190512.8151360844</v>
+        <v>201666.5274592238</v>
       </c>
       <c r="D36" s="14" t="n">
-        <v>11243.97115698428</v>
+        <v>4663.268356379209</v>
       </c>
       <c r="E36" s="20" t="n">
-        <v>0.1712974911074925</v>
+        <v>0.1584053222761093</v>
       </c>
       <c r="F36" s="44" t="n">
-        <v>1.784266631690435</v>
+        <v>1.720920304966544</v>
       </c>
       <c r="G36" s="14" t="n">
         <v>254292.9392258411</v>
@@ -22561,16 +22561,16 @@
         </is>
       </c>
       <c r="C37" s="14" t="n">
-        <v>413588.9774327216</v>
+        <v>417815.4889209859</v>
       </c>
       <c r="D37" s="14" t="n">
-        <v>-219818.8809063803</v>
+        <v>-222342.4213818359</v>
       </c>
       <c r="E37" s="20" t="n">
-        <v>-0.135906607260189</v>
+        <v>-0.1364609661570767</v>
       </c>
       <c r="F37" s="44" t="n">
-        <v>0.5967654421556489</v>
+        <v>0.5955624243216509</v>
       </c>
       <c r="G37" s="14" t="n">
         <v>176158.7977303777</v>
@@ -22579,23 +22579,23 @@
     <row r="38">
       <c r="B38" s="12" t="inlineStr">
         <is>
-          <t>Solo los 5 productos que pagan su registro</t>
+          <t>Solo los 4 productos que pagan su registro</t>
         </is>
       </c>
       <c r="C38" s="14" t="n">
-        <v>337046.6509166752</v>
+        <v>346807.6807167808</v>
       </c>
       <c r="D38" s="14" t="n">
-        <v>-158968.7625067845</v>
+        <v>-157705.836139263</v>
       </c>
       <c r="E38" s="20" t="n">
-        <v>-0.1133778797375236</v>
+        <v>-0.1064771796749633</v>
       </c>
       <c r="F38" s="44" t="n">
-        <v>0.6697550803343414</v>
+        <v>0.6913624721566353</v>
       </c>
       <c r="G38" s="14" t="n">
-        <v>132929.7214791037</v>
+        <v>133525.4698313464</v>
       </c>
     </row>
   </sheetData>
@@ -22707,25 +22707,25 @@
         <v>0.28735</v>
       </c>
       <c r="F5" s="20" t="n">
-        <v>0.9896</v>
+        <v>0.98995</v>
       </c>
       <c r="G5" s="20" t="n">
-        <v>0.98885</v>
+        <v>0.98915</v>
       </c>
       <c r="H5" s="14" t="n">
-        <v>-237706.4104814813</v>
+        <v>-241526.7622155904</v>
       </c>
       <c r="I5" s="44" t="n">
-        <v>0.3367461992769273</v>
+        <v>0.3440803101411151</v>
       </c>
       <c r="J5" s="14" t="n">
-        <v>395743.8029260205</v>
+        <v>403969.9119002493</v>
       </c>
       <c r="K5" s="14" t="n">
-        <v>505808.977519416</v>
+        <v>512914.5984385405</v>
       </c>
       <c r="L5" s="14" t="n">
-        <v>572967.5568419021</v>
+        <v>580249.1994396027</v>
       </c>
     </row>
     <row r="6">
@@ -22744,25 +22744,25 @@
         <v>0.10465</v>
       </c>
       <c r="F6" s="20" t="n">
-        <v>0.9916</v>
+        <v>0.99205</v>
       </c>
       <c r="G6" s="20" t="n">
-        <v>0.78815</v>
+        <v>0.7883</v>
       </c>
       <c r="H6" s="14" t="n">
-        <v>-160193.3489744359</v>
+        <v>-161936.8206150695</v>
       </c>
       <c r="I6" s="44" t="n">
-        <v>0.1610441622231673</v>
+        <v>0.174679404790704</v>
       </c>
       <c r="J6" s="14" t="n">
-        <v>271273.0996875869</v>
+        <v>277612.2682818624</v>
       </c>
       <c r="K6" s="14" t="n">
-        <v>465305.1989493736</v>
+        <v>472130.2679514411</v>
       </c>
       <c r="L6" s="14" t="n">
-        <v>543697.3520691571</v>
+        <v>549283.6979399872</v>
       </c>
     </row>
     <row r="7">
@@ -22781,25 +22781,25 @@
         <v>0.12405</v>
       </c>
       <c r="F7" s="20" t="n">
-        <v>0.9762999999999999</v>
+        <v>0.97695</v>
       </c>
       <c r="G7" s="20" t="n">
-        <v>0.8547</v>
+        <v>0.8555</v>
       </c>
       <c r="H7" s="14" t="n">
-        <v>-171666.6300264048</v>
+        <v>-173847.8846222783</v>
       </c>
       <c r="I7" s="44" t="n">
-        <v>0.2096173668514546</v>
+        <v>0.230564323018647</v>
       </c>
       <c r="J7" s="14" t="n">
-        <v>325874.5511436212</v>
+        <v>333236.1750197956</v>
       </c>
       <c r="K7" s="14" t="n">
-        <v>460480.9254471749</v>
+        <v>465974.9616357227</v>
       </c>
       <c r="L7" s="14" t="n">
-        <v>523288.2062519112</v>
+        <v>529575.1878087877</v>
       </c>
     </row>
     <row r="8">
@@ -22818,25 +22818,25 @@
         <v>0.12425</v>
       </c>
       <c r="F8" s="20" t="n">
-        <v>0.9297</v>
+        <v>0.93165</v>
       </c>
       <c r="G8" s="20" t="n">
-        <v>0.80535</v>
+        <v>0.8075</v>
       </c>
       <c r="H8" s="14" t="n">
-        <v>-120020.456104806</v>
+        <v>-122193.2434093025</v>
       </c>
       <c r="I8" s="44" t="n">
-        <v>0.2486911784384737</v>
+        <v>0.2733155935891806</v>
       </c>
       <c r="J8" s="14" t="n">
-        <v>245953.0522669783</v>
+        <v>252401.901965895</v>
       </c>
       <c r="K8" s="14" t="n">
-        <v>365369.8500770252</v>
+        <v>371373.9411225899</v>
       </c>
       <c r="L8" s="14" t="n">
-        <v>421174.7470299811</v>
+        <v>427004.6966737359</v>
       </c>
     </row>
     <row r="9">
@@ -22892,25 +22892,25 @@
         <v>0.15245</v>
       </c>
       <c r="F10" s="20" t="n">
-        <v>0.6434</v>
+        <v>0.6506999999999999</v>
       </c>
       <c r="G10" s="20" t="n">
-        <v>0.5129</v>
+        <v>0.5206499999999999</v>
       </c>
       <c r="H10" s="14" t="n">
-        <v>-86430.2435674015</v>
+        <v>-91177.33801870118</v>
       </c>
       <c r="I10" s="44" t="n">
-        <v>0.7865383864366985</v>
+        <v>0.7843474134698976</v>
       </c>
       <c r="J10" s="14" t="n">
-        <v>265330.3034204586</v>
+        <v>276770.3379435123</v>
       </c>
       <c r="K10" s="14" t="n">
-        <v>347563.0030544444</v>
+        <v>357822.6206962983</v>
       </c>
       <c r="L10" s="14" t="n">
-        <v>394436.6222243839</v>
+        <v>404224.7741828827</v>
       </c>
     </row>
     <row r="11">
@@ -22929,25 +22929,25 @@
         <v>0.12425</v>
       </c>
       <c r="F11" s="20" t="n">
-        <v>0.8174</v>
+        <v>0.8207</v>
       </c>
       <c r="G11" s="20" t="n">
-        <v>0.68835</v>
+        <v>0.69235</v>
       </c>
       <c r="H11" s="14" t="n">
-        <v>-85900.26435107071</v>
+        <v>-88105.31315460615</v>
       </c>
       <c r="I11" s="44" t="n">
-        <v>0.3164058038619845</v>
+        <v>0.350534876772312</v>
       </c>
       <c r="J11" s="14" t="n">
-        <v>193512.1033986795</v>
+        <v>200522.709050072</v>
       </c>
       <c r="K11" s="14" t="n">
-        <v>302524.5082425199</v>
+        <v>309097.2732595108</v>
       </c>
       <c r="L11" s="14" t="n">
-        <v>355386.3974776263</v>
+        <v>360578.5974124155</v>
       </c>
     </row>
     <row r="12">
@@ -22966,25 +22966,25 @@
         <v>0.15245</v>
       </c>
       <c r="F12" s="20" t="n">
-        <v>0.47725</v>
+        <v>0.4837</v>
       </c>
       <c r="G12" s="20" t="n">
-        <v>0.3489</v>
+        <v>0.3548</v>
       </c>
       <c r="H12" s="14" t="n">
-        <v>-49841.526665891</v>
+        <v>-54632.98149840152</v>
       </c>
       <c r="I12" s="44" t="n">
-        <v>1.043323573382448</v>
+        <v>1.030968418784095</v>
       </c>
       <c r="J12" s="14" t="n">
-        <v>217353.9229290343</v>
+        <v>227974.6991998056</v>
       </c>
       <c r="K12" s="14" t="n">
-        <v>294686.8559203281</v>
+        <v>305022.8707870186</v>
       </c>
       <c r="L12" s="14" t="n">
-        <v>340540.9281549089</v>
+        <v>349159.3558588034</v>
       </c>
     </row>
     <row r="13">
@@ -23003,25 +23003,25 @@
         <v>0.12425</v>
       </c>
       <c r="F13" s="20" t="n">
-        <v>0.9405</v>
+        <v>0.94335</v>
       </c>
       <c r="G13" s="20" t="n">
-        <v>0.8167</v>
+        <v>0.8192</v>
       </c>
       <c r="H13" s="14" t="n">
-        <v>-131027.1227140213</v>
+        <v>-134244.3090683899</v>
       </c>
       <c r="I13" s="44" t="n">
-        <v>0.3007484006981544</v>
+        <v>0.3404908782335647</v>
       </c>
       <c r="J13" s="14" t="n">
-        <v>292028.0232186471</v>
+        <v>304425.9866690554</v>
       </c>
       <c r="K13" s="14" t="n">
-        <v>439506.5798115571</v>
+        <v>447792.3349017084</v>
       </c>
       <c r="L13" s="14" t="n">
-        <v>505801.0069430012</v>
+        <v>513132.9910763496</v>
       </c>
     </row>
     <row r="14">
@@ -23040,25 +23040,25 @@
         <v>0.06645</v>
       </c>
       <c r="F14" s="20" t="n">
-        <v>0.95475</v>
+        <v>0.9560999999999999</v>
       </c>
       <c r="G14" s="20" t="n">
-        <v>0.4298</v>
+        <v>0.43115</v>
       </c>
       <c r="H14" s="14" t="n">
-        <v>-66220.83287140375</v>
+        <v>-67456.73441016677</v>
       </c>
       <c r="I14" s="44" t="n">
         <v>0</v>
       </c>
       <c r="J14" s="14" t="n">
-        <v>253267.5502123729</v>
+        <v>260841.8658228375</v>
       </c>
       <c r="K14" s="14" t="n">
-        <v>365632.3074752419</v>
+        <v>372063.1097380665</v>
       </c>
       <c r="L14" s="14" t="n">
-        <v>421025.4148123499</v>
+        <v>426928.0466689822</v>
       </c>
     </row>
     <row r="15">
@@ -23114,19 +23114,19 @@
         </is>
       </c>
       <c r="C19" s="14" t="n">
-        <v>66658.12212496769</v>
+        <v>68018.42197487189</v>
       </c>
       <c r="D19" s="14" t="n">
-        <v>96169.72232115472</v>
+        <v>97363.87266841835</v>
       </c>
       <c r="E19" s="14" t="n">
-        <v>-39826.77066478981</v>
+        <v>-40438.78944855986</v>
       </c>
       <c r="F19" s="20" t="n">
-        <v>0.9903</v>
+        <v>0.9908</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>-21141.34092120263</v>
+        <v>-21429.05816790805</v>
       </c>
     </row>
     <row r="20">
@@ -23136,19 +23136,19 @@
         </is>
       </c>
       <c r="C20" s="14" t="n">
-        <v>45996.40539571895</v>
+        <v>47008.72846503975</v>
       </c>
       <c r="D20" s="14" t="n">
-        <v>91367.15086064125</v>
+        <v>92296.02758559588</v>
       </c>
       <c r="E20" s="14" t="n">
-        <v>-26146.43851189761</v>
+        <v>-26380.45891560251</v>
       </c>
       <c r="F20" s="20" t="n">
-        <v>0.9923</v>
+        <v>0.99275</v>
       </c>
       <c r="G20" s="14" t="n">
-        <v>-1332.876223538889</v>
+        <v>-1333.556532785007</v>
       </c>
     </row>
     <row r="21">
@@ -23158,19 +23158,19 @@
         </is>
       </c>
       <c r="C21" s="14" t="n">
-        <v>55020.04141683297</v>
+        <v>56269.83590610274</v>
       </c>
       <c r="D21" s="14" t="n">
-        <v>87986.11219062147</v>
+        <v>88978.27423035786</v>
       </c>
       <c r="E21" s="14" t="n">
-        <v>-26744.11233597222</v>
+        <v>-27045.89284831961</v>
       </c>
       <c r="F21" s="20" t="n">
-        <v>0.9781</v>
+        <v>0.97865</v>
       </c>
       <c r="G21" s="14" t="n">
-        <v>-1536.034099684545</v>
+        <v>-1545.09750526303</v>
       </c>
     </row>
     <row r="22">
@@ -23180,19 +23180,19 @@
         </is>
       </c>
       <c r="C22" s="14" t="n">
-        <v>41693.71689242253</v>
+        <v>42752.98090071263</v>
       </c>
       <c r="D22" s="14" t="n">
-        <v>70909.94331673883</v>
+        <v>71900.89932785562</v>
       </c>
       <c r="E22" s="14" t="n">
-        <v>-17884.34523690179</v>
+        <v>-18183.61347526393</v>
       </c>
       <c r="F22" s="20" t="n">
-        <v>0.93425</v>
+        <v>0.9360000000000001</v>
       </c>
       <c r="G22" s="14" t="n">
-        <v>-1106.111408872155</v>
+        <v>-1123.743066108145</v>
       </c>
     </row>
     <row r="23">
@@ -23224,19 +23224,19 @@
         </is>
       </c>
       <c r="C24" s="14" t="n">
-        <v>44937.33064547902</v>
+        <v>46840.95424086895</v>
       </c>
       <c r="D24" s="14" t="n">
-        <v>66463.97047156046</v>
+        <v>68090.77903400685</v>
       </c>
       <c r="E24" s="14" t="n">
-        <v>-5191.119787438914</v>
+        <v>-5844.529292587128</v>
       </c>
       <c r="F24" s="20" t="n">
-        <v>0.65615</v>
+        <v>0.6625</v>
       </c>
       <c r="G24" s="14" t="n">
-        <v>18417.70996737284</v>
+        <v>17968.78498919589</v>
       </c>
     </row>
     <row r="25">
@@ -23246,19 +23246,19 @@
         </is>
       </c>
       <c r="C25" s="14" t="n">
-        <v>32958.70223899107</v>
+        <v>34118.04034298623</v>
       </c>
       <c r="D25" s="14" t="n">
-        <v>59892.64718410921</v>
+        <v>60776.68794187457</v>
       </c>
       <c r="E25" s="14" t="n">
-        <v>-10184.00874941214</v>
+        <v>-10478.32917369867</v>
       </c>
       <c r="F25" s="20" t="n">
-        <v>0.82655</v>
+        <v>0.8300999999999999</v>
       </c>
       <c r="G25" s="14" t="n">
-        <v>6196.392609327573</v>
+        <v>5941.696201418631</v>
       </c>
     </row>
     <row r="26">
@@ -23268,19 +23268,19 @@
         </is>
       </c>
       <c r="C26" s="14" t="n">
-        <v>36954.53618703249</v>
+        <v>38713.8915504849</v>
       </c>
       <c r="D26" s="14" t="n">
-        <v>57535.57121905119</v>
+        <v>58891.03006631183</v>
       </c>
       <c r="E26" s="14" t="n">
-        <v>3065.21136622687</v>
+        <v>2420.584325522921</v>
       </c>
       <c r="F26" s="20" t="n">
-        <v>0.4871</v>
+        <v>0.4926</v>
       </c>
       <c r="G26" s="14" t="n">
-        <v>28445.55824299242</v>
+        <v>27957.53571995132</v>
       </c>
     </row>
     <row r="27">
@@ -23290,19 +23290,19 @@
         </is>
       </c>
       <c r="C27" s="14" t="n">
-        <v>49445.78535571039</v>
+        <v>51469.20735156454</v>
       </c>
       <c r="D27" s="14" t="n">
-        <v>84959.07913252991</v>
+        <v>86207.70283543823</v>
       </c>
       <c r="E27" s="14" t="n">
-        <v>-18937.6116460146</v>
+        <v>-19361.12055964272</v>
       </c>
       <c r="F27" s="20" t="n">
-        <v>0.9449</v>
+        <v>0.947</v>
       </c>
       <c r="G27" s="14" t="n">
-        <v>-1191.366429928346</v>
+        <v>-1212.926316191447</v>
       </c>
     </row>
     <row r="28">
@@ -23312,19 +23312,19 @@
         </is>
       </c>
       <c r="C28" s="14" t="n">
-        <v>42878.5076437429</v>
+        <v>44155.24365537205</v>
       </c>
       <c r="D28" s="14" t="n">
-        <v>70971.4028957281</v>
+        <v>71879.40164983823</v>
       </c>
       <c r="E28" s="14" t="n">
-        <v>-9931.157596173745</v>
+        <v>-10101.26665813037</v>
       </c>
       <c r="F28" s="20" t="n">
-        <v>0.9577</v>
+        <v>0.95885</v>
       </c>
       <c r="G28" s="14" t="n">
-        <v>-935.2402058026985</v>
+        <v>-937.5842042166602</v>
       </c>
     </row>
     <row r="29">
@@ -23334,19 +23334,19 @@
         </is>
       </c>
       <c r="C29" s="14" t="n">
-        <v>25534.24486582657</v>
+        <v>26199.27450405085</v>
       </c>
       <c r="D29" s="14" t="n">
-        <v>43184.72673467203</v>
+        <v>43752.01367669849</v>
       </c>
       <c r="E29" s="14" t="n">
-        <v>-2929.068004114983</v>
+        <v>-2909.686902555771</v>
       </c>
       <c r="F29" s="20" t="n">
-        <v>0.71405</v>
+        <v>0.7129</v>
       </c>
       <c r="G29" s="14" t="n">
-        <v>17568.16347331521</v>
+        <v>17536.87206075913</v>
       </c>
     </row>
     <row r="30">
@@ -23356,19 +23356,19 @@
         </is>
       </c>
       <c r="C30" s="14" t="n">
-        <v>17465.40912407408</v>
+        <v>17889.13041669067</v>
       </c>
       <c r="D30" s="14" t="n">
-        <v>29259.23450164852</v>
+        <v>29653.16765019082</v>
       </c>
       <c r="E30" s="14" t="n">
-        <v>4548.57061227842</v>
+        <v>4727.276383798304</v>
       </c>
       <c r="F30" s="20" t="n">
-        <v>0.60815</v>
+        <v>0.60555</v>
       </c>
       <c r="G30" s="14" t="n">
-        <v>29166.51839935734</v>
+        <v>29399.0204954875</v>
       </c>
     </row>
     <row r="32">
@@ -23455,7 +23455,7 @@
     <row r="2">
       <c r="B2" s="10" t="inlineStr">
         <is>
-          <t>VPN base: B/.-196,169. Capital base: B/.388,711.</t>
+          <t>VPN base: B/.-198,693. Capital base: B/.392,938.</t>
         </is>
       </c>
     </row>
@@ -23514,20 +23514,20 @@
         <v>2986</v>
       </c>
       <c r="E5" s="14" t="n">
-        <v>-325595.7660578114</v>
+        <v>-328447.4134030846</v>
       </c>
       <c r="F5" s="14" t="n">
-        <v>-136194.0986232299</v>
+        <v>-138267.7788415737</v>
       </c>
       <c r="G5" s="14">
         <f>F5-E5</f>
         <v/>
       </c>
       <c r="H5" s="14" t="n">
-        <v>545267.3461994913</v>
+        <v>546099.5265205839</v>
       </c>
       <c r="I5" s="14" t="n">
-        <v>329528.5625527216</v>
+        <v>329838.4049414305</v>
       </c>
     </row>
     <row r="6">
@@ -23543,20 +23543,20 @@
         <v>1</v>
       </c>
       <c r="E6" s="14" t="n">
-        <v>-221179.2742578355</v>
+        <v>-223892.3336772754</v>
       </c>
       <c r="F6" s="14" t="n">
-        <v>-167102.3389237261</v>
+        <v>-169432.5379766415</v>
       </c>
       <c r="G6" s="14">
         <f>F6-E6</f>
         <v/>
       </c>
       <c r="H6" s="14" t="n">
-        <v>367904.0795321364</v>
+        <v>368864.9604528522</v>
       </c>
       <c r="I6" s="14" t="n">
-        <v>371842.6776486586</v>
+        <v>372190.8062493597</v>
       </c>
     </row>
     <row r="7">
@@ -23572,20 +23572,20 @@
         <v>0</v>
       </c>
       <c r="E7" s="14" t="n">
-        <v>-221540.2563641068</v>
+        <v>-224421.4160726953</v>
       </c>
       <c r="F7" s="14" t="n">
-        <v>-170281.5458652293</v>
+        <v>-172355.4761291275</v>
       </c>
       <c r="G7" s="14">
         <f>F7-E7</f>
         <v/>
       </c>
       <c r="H7" s="14" t="n">
-        <v>405375.7537044846</v>
+        <v>409187.2656907371</v>
       </c>
       <c r="I7" s="14" t="n">
-        <v>380080.1523504786</v>
+        <v>380389.9947391875</v>
       </c>
     </row>
     <row r="8">
@@ -23601,78 +23601,78 @@
         <v>0.32</v>
       </c>
       <c r="E8" s="14" t="n">
-        <v>-223921.8810053787</v>
+        <v>-226885.797092441</v>
       </c>
       <c r="F8" s="14" t="n">
-        <v>-174119.549674342</v>
+        <v>-176193.4799382402</v>
       </c>
       <c r="G8" s="14">
         <f>F8-E8</f>
         <v/>
       </c>
       <c r="H8" s="14" t="n">
-        <v>405034.9108497411</v>
+        <v>408864.0591253622</v>
       </c>
       <c r="I8" s="14" t="n">
-        <v>383587.9304066129</v>
+        <v>383897.7727953219</v>
       </c>
     </row>
     <row r="9">
       <c r="B9" s="12" t="inlineStr">
         <is>
-          <t>Parte de la cantidad de la compra conjunta de 2023 que se toma como demanda del MINSA</t>
+          <t>Colateral en efectivo que pide la aseguradora o el banco (% de la fianza)</t>
         </is>
       </c>
       <c r="C9" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D9" s="9" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="E9" s="14" t="n">
-        <v>-207342.9656046493</v>
+        <v>-211852.12420573</v>
       </c>
       <c r="F9" s="14" t="n">
-        <v>-170504.1893428613</v>
+        <v>-172572.5748813284</v>
       </c>
       <c r="G9" s="14">
         <f>F9-E9</f>
         <v/>
       </c>
       <c r="H9" s="14" t="n">
-        <v>393035.5944346618</v>
+        <v>434212.7724614988</v>
       </c>
       <c r="I9" s="14" t="n">
-        <v>384541.5579698699</v>
+        <v>312118.0112346699</v>
       </c>
     </row>
     <row r="10">
       <c r="B10" s="12" t="inlineStr">
         <is>
-          <t>Colateral en efectivo que pide la aseguradora o el banco (% de la fianza)</t>
+          <t>Parte de la cantidad de la compra conjunta de 2023 que se toma como demanda del MINSA</t>
         </is>
       </c>
       <c r="C10" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D10" s="9" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="E10" s="14" t="n">
-        <v>-208424.1366835031</v>
+        <v>-210168.0876932347</v>
       </c>
       <c r="F10" s="14" t="n">
-        <v>-171659.381970746</v>
+        <v>-172578.1196067595</v>
       </c>
       <c r="G10" s="14">
         <f>F10-E10</f>
         <v/>
       </c>
       <c r="H10" s="14" t="n">
-        <v>427163.131726102</v>
+        <v>398786.3037511055</v>
       </c>
       <c r="I10" s="14" t="n">
-        <v>311808.1688459609</v>
+        <v>384851.4003585788</v>
       </c>
     </row>
     <row r="11">
@@ -23688,20 +23688,20 @@
         <v>0.45</v>
       </c>
       <c r="E11" s="14" t="n">
-        <v>-212667.3310390303</v>
+        <v>-216865.7144601127</v>
       </c>
       <c r="F11" s="14" t="n">
-        <v>-184510.6513406656</v>
+        <v>-186584.5816045638</v>
       </c>
       <c r="G11" s="14">
         <f>F11-E11</f>
         <v/>
       </c>
       <c r="H11" s="14" t="n">
-        <v>350090.1738452589</v>
+        <v>366102.8738230804</v>
       </c>
       <c r="I11" s="14" t="n">
-        <v>456683.3735659856</v>
+        <v>456993.2159546945</v>
       </c>
     </row>
     <row r="12">
@@ -23717,20 +23717,20 @@
         <v>12</v>
       </c>
       <c r="E12" s="14" t="n">
-        <v>-182831.2476934687</v>
+        <v>-185654.2314283854</v>
       </c>
       <c r="F12" s="14" t="n">
-        <v>-210065.704971832</v>
+        <v>-212540.7872288765</v>
       </c>
       <c r="G12" s="14">
         <f>F12-E12</f>
         <v/>
       </c>
       <c r="H12" s="14" t="n">
-        <v>316130.3130422327</v>
+        <v>319237.5369424171</v>
       </c>
       <c r="I12" s="14" t="n">
-        <v>465761.4101030089</v>
+        <v>467461.204451691</v>
       </c>
     </row>
     <row r="13">
@@ -23746,20 +23746,20 @@
         <v>0.9</v>
       </c>
       <c r="E13" s="14" t="n">
-        <v>-208686.1414664519</v>
+        <v>-211575.2973605898</v>
       </c>
       <c r="F13" s="14" t="n">
-        <v>-186938.2427279398</v>
+        <v>-189096.4365311863</v>
       </c>
       <c r="G13" s="14">
         <f>F13-E13</f>
         <v/>
       </c>
       <c r="H13" s="14" t="n">
-        <v>384784.3430653527</v>
+        <v>391110.2780902667</v>
       </c>
       <c r="I13" s="14" t="n">
-        <v>393393.5402108126</v>
+        <v>394437.4237585106</v>
       </c>
     </row>
     <row r="14">
@@ -23775,78 +23775,78 @@
         <v>105</v>
       </c>
       <c r="E14" s="14" t="n">
-        <v>-210962.0431875669</v>
+        <v>-214445.9545827128</v>
       </c>
       <c r="F14" s="14" t="n">
-        <v>-190894.7116902138</v>
+        <v>-193003.3384886285</v>
       </c>
       <c r="G14" s="14">
         <f>F14-E14</f>
         <v/>
       </c>
       <c r="H14" s="14" t="n">
-        <v>437389.3340354656</v>
+        <v>447565.7161035886</v>
       </c>
       <c r="I14" s="14" t="n">
-        <v>373901.0024359346</v>
+        <v>374513.0951764134</v>
       </c>
     </row>
     <row r="15">
       <c r="B15" s="12" t="inlineStr">
         <is>
-          <t>Factor de mercado (demanda futura frente a 2025-2026)</t>
+          <t>Precio de oferta descentralizado frente al precio ponderado actual</t>
         </is>
       </c>
       <c r="C15" s="9" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="D15" s="9" t="n">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="E15" s="14" t="n">
-        <v>-207589.7430260061</v>
+        <v>-210990.939067518</v>
       </c>
       <c r="F15" s="14" t="n">
-        <v>-188876.2733657533</v>
+        <v>-191914.6191428568</v>
       </c>
       <c r="G15" s="14">
         <f>F15-E15</f>
         <v/>
       </c>
       <c r="H15" s="14" t="n">
-        <v>372283.9111989561</v>
+        <v>403653.6489255751</v>
       </c>
       <c r="I15" s="14" t="n">
-        <v>402667.1341608018</v>
+        <v>388683.617572016</v>
       </c>
     </row>
     <row r="16">
       <c r="B16" s="12" t="inlineStr">
         <is>
-          <t>Precio de oferta descentralizado frente al precio ponderado actual</t>
+          <t>Factor de mercado (demanda futura frente a 2025-2026)</t>
         </is>
       </c>
       <c r="C16" s="9" t="n">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="D16" s="9" t="n">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="E16" s="14" t="n">
-        <v>-208077.1864868201</v>
+        <v>-210044.6940082464</v>
       </c>
       <c r="F16" s="14" t="n">
-        <v>-189618.1141734695</v>
+        <v>-191303.1413229703</v>
       </c>
       <c r="G16" s="14">
         <f>F16-E16</f>
         <v/>
       </c>
       <c r="H16" s="14" t="n">
-        <v>396027.9003746543</v>
+        <v>376847.7379807483</v>
       </c>
       <c r="I16" s="14" t="n">
-        <v>386434.8702186889</v>
+        <v>404078.5408787696</v>
       </c>
     </row>
     <row r="17">
@@ -23862,20 +23862,20 @@
         <v>1000</v>
       </c>
       <c r="E17" s="14" t="n">
-        <v>-203912.9855545087</v>
+        <v>-206436.5260299644</v>
       </c>
       <c r="F17" s="14" t="n">
-        <v>-188425.4513373261</v>
+        <v>-190948.9918127817</v>
       </c>
       <c r="G17" s="14">
         <f>F17-E17</f>
         <v/>
       </c>
       <c r="H17" s="14" t="n">
-        <v>397211.4774327216</v>
+        <v>401437.9889209859</v>
       </c>
       <c r="I17" s="14" t="n">
-        <v>380211.4774327216</v>
+        <v>384437.9889209859</v>
       </c>
     </row>
     <row r="18">
@@ -23891,20 +23891,20 @@
         <v>0.95</v>
       </c>
       <c r="E18" s="14" t="n">
-        <v>-204711.4581116569</v>
+        <v>-207129.1996762248</v>
       </c>
       <c r="F18" s="14" t="n">
-        <v>-190725.986894023</v>
+        <v>-193201.1271640944</v>
       </c>
       <c r="G18" s="14">
         <f>F18-E18</f>
         <v/>
       </c>
       <c r="H18" s="14" t="n">
-        <v>367193.1056002061</v>
+        <v>371971.4999129465</v>
       </c>
       <c r="I18" s="14" t="n">
-        <v>405503.0551448065</v>
+        <v>407218.9174645216</v>
       </c>
     </row>
     <row r="19">
@@ -23920,20 +23920,20 @@
         <v>0.015</v>
       </c>
       <c r="E19" s="14" t="n">
-        <v>-203682.2177255959</v>
+        <v>-206465.3745804783</v>
       </c>
       <c r="F19" s="14" t="n">
-        <v>-191473.9385532266</v>
+        <v>-193835.2187915406</v>
       </c>
       <c r="G19" s="14">
         <f>F19-E19</f>
         <v/>
       </c>
       <c r="H19" s="14" t="n">
-        <v>394964.1346502588</v>
+        <v>401452.2305618773</v>
       </c>
       <c r="I19" s="14" t="n">
-        <v>384803.5666717609</v>
+        <v>387616.5878954289</v>
       </c>
     </row>
     <row r="20">
@@ -23949,20 +23949,20 @@
         <v>120</v>
       </c>
       <c r="E20" s="14" t="n">
-        <v>-196169.2184459174</v>
+        <v>-198692.758921373</v>
       </c>
       <c r="F20" s="14" t="n">
-        <v>-186555.8360268903</v>
+        <v>-189024.9765651919</v>
       </c>
       <c r="G20" s="14">
         <f>F20-E20</f>
         <v/>
       </c>
       <c r="H20" s="14" t="n">
-        <v>388711.4774327216</v>
+        <v>392937.988920986</v>
       </c>
       <c r="I20" s="14" t="n">
-        <v>361232.6256981902</v>
+        <v>364985.2454744953</v>
       </c>
     </row>
     <row r="21">
@@ -23978,20 +23978,20 @@
         <v>0.7</v>
       </c>
       <c r="E21" s="14" t="n">
-        <v>-200570.4120640938</v>
+        <v>-203280.4334356618</v>
       </c>
       <c r="F21" s="14" t="n">
-        <v>-191768.0248277409</v>
+        <v>-194105.0844070842</v>
       </c>
       <c r="G21" s="14">
         <f>F21-E21</f>
         <v/>
       </c>
       <c r="H21" s="14" t="n">
-        <v>389426.3207692105</v>
+        <v>395277.3148530337</v>
       </c>
       <c r="I21" s="14" t="n">
-        <v>387996.6340962327</v>
+        <v>390598.6629889381</v>
       </c>
     </row>
     <row r="22">
@@ -24007,78 +24007,78 @@
         <v>9</v>
       </c>
       <c r="E22" s="14" t="n">
-        <v>-201369.0712033912</v>
+        <v>-204202.9471275882</v>
       </c>
       <c r="F22" s="14" t="n">
-        <v>-193343.132904571</v>
+        <v>-195726.7662051287</v>
       </c>
       <c r="G22" s="14">
         <f>F22-E22</f>
         <v/>
       </c>
       <c r="H22" s="14" t="n">
-        <v>394287.1229588037</v>
+        <v>401217.0456048609</v>
       </c>
       <c r="I22" s="14" t="n">
-        <v>385432.2187848369</v>
+        <v>388439.9632285736</v>
       </c>
     </row>
     <row r="23">
       <c r="B23" s="12" t="inlineStr">
         <is>
-          <t>Mes en que salen los registros sanitarios (presentados en el mes 3)</t>
+          <t>Multiplicador del costo logístico (flete LCL, destino, corredor, seguro)</t>
         </is>
       </c>
       <c r="C23" s="9" t="n">
-        <v>12</v>
+        <v>2.2</v>
       </c>
       <c r="D23" s="9" t="n">
-        <v>7</v>
+        <v>0.8</v>
       </c>
       <c r="E23" s="14" t="n">
-        <v>-199984.1813126385</v>
+        <v>-192682.3786853023</v>
       </c>
       <c r="F23" s="14" t="n">
-        <v>-193406.3110268089</v>
+        <v>-185695.9571421767</v>
       </c>
       <c r="G23" s="14">
         <f>F23-E23</f>
         <v/>
       </c>
       <c r="H23" s="14" t="n">
-        <v>393177.8385621419</v>
+        <v>294539.9275341209</v>
       </c>
       <c r="I23" s="14" t="n">
-        <v>384985.2222519561</v>
+        <v>399212.6039981513</v>
       </c>
     </row>
     <row r="24">
       <c r="B24" s="12" t="inlineStr">
         <is>
-          <t>Multiplicador del costo logístico (flete LCL, destino, corredor, seguro)</t>
+          <t>Mes en que salen los registros sanitarios (presentados en el mes 3)</t>
         </is>
       </c>
       <c r="C24" s="9" t="n">
-        <v>2.2</v>
+        <v>12</v>
       </c>
       <c r="D24" s="9" t="n">
-        <v>0.8</v>
+        <v>7</v>
       </c>
       <c r="E24" s="14" t="n">
-        <v>-190130.6042199839</v>
+        <v>-202792.0710730963</v>
       </c>
       <c r="F24" s="14" t="n">
-        <v>-183622.0268782785</v>
+        <v>-195831.0546674679</v>
       </c>
       <c r="G24" s="14">
         <f>F24-E24</f>
         <v/>
       </c>
       <c r="H24" s="14" t="n">
-        <v>292499.4493694881</v>
+        <v>399881.3891154018</v>
       </c>
       <c r="I24" s="14" t="n">
-        <v>398902.7616094422</v>
+        <v>388351.0893419504</v>
       </c>
     </row>
     <row r="25">
@@ -24094,78 +24094,78 @@
         <v>0.013</v>
       </c>
       <c r="E25" s="14" t="n">
-        <v>-198892.1535687828</v>
+        <v>-201681.1217384212</v>
       </c>
       <c r="F25" s="14" t="n">
-        <v>-193990.8703476251</v>
+        <v>-196302.0686677346</v>
       </c>
       <c r="G25" s="14">
         <f>F25-E25</f>
         <v/>
       </c>
       <c r="H25" s="14" t="n">
-        <v>390888.9735585285</v>
+        <v>395874.0087297743</v>
       </c>
       <c r="I25" s="14" t="n">
-        <v>386969.4805320761</v>
+        <v>390589.1730739553</v>
       </c>
     </row>
     <row r="26">
       <c r="B26" s="12" t="inlineStr">
         <is>
-          <t>Mes en que podría arrancar el primer contrato centralizado (calendario de la LPU)</t>
+          <t>Anticipo a la fábrica al colocar la orden</t>
         </is>
       </c>
       <c r="C26" s="9" t="n">
-        <v>27</v>
+        <v>1</v>
       </c>
       <c r="D26" s="9" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="E26" s="14" t="n">
-        <v>-197061.4789206212</v>
+        <v>-201103.2848507945</v>
       </c>
       <c r="F26" s="14" t="n">
-        <v>-192199.2100492774</v>
+        <v>-197659.6763801925</v>
       </c>
       <c r="G26" s="14">
         <f>F26-E26</f>
         <v/>
       </c>
       <c r="H26" s="14" t="n">
-        <v>403601.9837677054</v>
+        <v>399933.9680260378</v>
       </c>
       <c r="I26" s="14" t="n">
-        <v>371220.0609974038</v>
+        <v>389939.712161678</v>
       </c>
     </row>
     <row r="27">
       <c r="B27" s="12" t="inlineStr">
         <is>
-          <t>Anticipo a la fábrica al colocar la orden</t>
+          <t>Mes en que podría arrancar el primer contrato centralizado (calendario de la LPU)</t>
         </is>
       </c>
       <c r="C27" s="9" t="n">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="D27" s="9" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="E27" s="14" t="n">
-        <v>-198563.9973831404</v>
+        <v>-198702.4909615664</v>
       </c>
       <c r="F27" s="14" t="n">
-        <v>-195142.884615679</v>
+        <v>-195869.8506610747</v>
       </c>
       <c r="G27" s="14">
         <f>F27-E27</f>
         <v/>
       </c>
       <c r="H27" s="14" t="n">
-        <v>395570.2804768902</v>
+        <v>408914.1351236388</v>
       </c>
       <c r="I27" s="14" t="n">
-        <v>385771.9904137922</v>
+        <v>383615.0173086413</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/Modelo_financiero.xlsx
+++ b/outputs/Modelo_financiero.xlsx
@@ -2103,7 +2103,7 @@
       </c>
       <c r="H29" s="15" t="inlineStr">
         <is>
-          <t>F: el pliego exige 18 meses de vida útil al entregar; con 24 meses de vida útil quedan unos 3 meses de ventana en bodega; E: frecuencia</t>
+          <t>F: el pliego pide el vencimiento de la ficha técnica o, si no lo fija, 18 meses de vida útil al entregar; con 24 meses de vida útil quedan unos 3 meses de ventana en bodega; E: frecuencia</t>
         </is>
       </c>
     </row>
@@ -2208,7 +2208,7 @@
       </c>
       <c r="H32" s="15" t="inlineStr">
         <is>
-          <t>E: limitada por la vida útil (18 meses exigidos al entregar)</t>
+          <t>E: limitada por la vida útil exigida al entregar (18 meses si la ficha técnica no fija otra)</t>
         </is>
       </c>
     </row>
@@ -2628,7 +2628,7 @@
       </c>
       <c r="H44" s="15" t="inlineStr">
         <is>
-          <t>R: guía del MINSA de 2012 US$1,000; SignatureLex B/.1,500; la tarifa vigente no está publicada pese a la Ley 419 art. 79</t>
+          <t>R: guía del MINSA de 2012 US$1,000; SignatureLex B/.1,500; la tasa vigente no está publicada pese a la Ley 419 art. 79</t>
         </is>
       </c>
     </row>

--- a/outputs/Modelo_financiero.xlsx
+++ b/outputs/Modelo_financiero.xlsx
@@ -920,7 +920,7 @@
     <row r="1">
       <c r="B1" s="6" t="inlineStr">
         <is>
-          <t>Presupuesto de vida útil (regla de 18 meses al entregar)</t>
+          <t>Presupuesto de vida útil (pliego de la LPU: vencimiento de la ficha técnica; 18 meses si no lo fija)</t>
         </is>
       </c>
     </row>
@@ -937,7 +937,7 @@
     <row r="4">
       <c r="B4" s="9" t="inlineStr">
         <is>
-          <t>Vida útil mínima exigida al entregar (pliego de la LPU)</t>
+          <t>Vida útil exigida al entregar (18 meses si la ficha técnica no fija otra)</t>
         </is>
       </c>
       <c r="C4" s="46" t="n">
@@ -1473,7 +1473,7 @@
       </c>
       <c r="H11" s="15" t="inlineStr">
         <is>
-          <t>F: la LPU 01-2026 vence el 11-may-2027 y la siguiente se licitaría entre dic-2026 y feb-2027, antes de tener registros; la que sigue arrancaría hacia ago-2028 (mes 20). Optimista: la CSS prorroga y licita a inicios de 2028; pesimista: el calendario se corre 7 meses</t>
+          <t>F: la LPU 01-2026 vence el 11-may-2027; E: si se repite su ciclo, la siguiente se licita entre dic-2026 y feb-2027, antes de tener registros, y la que sigue arrancaría hacia ago-2028 (mes 20). Optimista: la CSS prorroga y licita a inicios de 2028; pesimista: el calendario se corre 7 meses</t>
         </is>
       </c>
     </row>

--- a/outputs/Modelo_financiero.xlsx
+++ b/outputs/Modelo_financiero.xlsx
@@ -2068,7 +2068,7 @@
       </c>
       <c r="H28" s="15" t="inlineStr">
         <is>
-          <t>F: multas de 5-15% y mora de al menos 10% (Ley 419 art. 231); E: frecuencia</t>
+          <t>F: multas de 5-15% y mora de al menos 10% (Ley 419 arts. 231 y 232); E: frecuencia</t>
         </is>
       </c>
     </row>

--- a/outputs/Modelo_financiero.xlsx
+++ b/outputs/Modelo_financiero.xlsx
@@ -4248,7 +4248,7 @@
       </c>
       <c r="B92" s="12" t="inlineStr">
         <is>
-          <t>Fase 0: opinión legal escrita sobre la Ley 316 (parentesco), de un abogado independiente</t>
+          <t>Fase 0: opinión legal escrita sobre la Ley 419, art. 249, y la Ley 316 (parentesco), de un abogado idóneo e independiente</t>
         </is>
       </c>
       <c r="C92" s="16" t="n">
